--- a/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,25 +507,25 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hQiNHHd2</t>
+          <t>hIoLKAg0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.8125</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19400</v>
+        <v>20371</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -569,30 +569,30 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>C6QBlj7R</t>
+          <t>KEflYcbt</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23112</v>
+        <v>68756</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -617,40 +617,40 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dbI3Q902</t>
+          <t>EyfhXHDn</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.85416666666</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bank of america stadium
-  charlotte  nc </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>74867</v>
+        <v>25000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -675,40 +675,40 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>zkH7PTF8</t>
+          <t>SvbdWyTh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.89583333334</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20000</v>
+        <v>61500</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>O6hjfSXE</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -733,40 +733,40 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UPVAOmVE</t>
+          <t>AoWGqXpJ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.89583333334</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21550</v>
+        <v>22039</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -793,42 +793,38 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>8GUEN7pL</t>
+          <t>trWntSE7</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.85416666666</v>
+        <v>45542.97916666666</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">yankee stadium
-  new york  ny </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>54251</v>
+        <v>54405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -853,608 +849,16 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>juKJMRaR</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45528.85416666666</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">subaru park
-  chester  pa </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>18500</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>167</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Usy7kWiL</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45528.85416666666</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>54405</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>167</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>lSHwpAFr</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>22039</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
           <t>2i4sdl32</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>167</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MNAkH5Nl</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>167</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>S0BoIo8r</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45528.89583333334</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>167</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>0E9gGPxe</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45528.9375</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>167</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Ik4bFqh1</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45528.97916666666</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>27000</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>167</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dt32E377</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45528.97916666666</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>167</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vqenBDBt</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45531.875</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>dtMNCXyk</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>167</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1672</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>us open cup</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>SWX9C8ZI</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45531.97916666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>167</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1672</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>us open cup</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -513,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mendoza r 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">lower com field
@@ -565,6 +640,34 @@
           <t>bm8usLzB</t>
         </is>
       </c>
+      <c r="P2" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>186</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>63</v>
+      </c>
+      <c r="U2" t="n">
+        <v>50000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>63</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -575,7 +678,12 @@
       <c r="B3" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">gillette stadium
@@ -622,6 +730,48 @@
         <is>
           <t>CURGfJWt</t>
         </is>
+      </c>
+      <c r="P3" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>179</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>78</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X3" t="n">
+        <v>177</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>129</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1975000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="4">
@@ -633,7 +783,12 @@
       <c r="B4" s="2" t="n">
         <v>45542.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">red bull arena
@@ -680,6 +835,48 @@
         <is>
           <t>2i4sdl32</t>
         </is>
+      </c>
+      <c r="P4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>185</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>50</v>
+      </c>
+      <c r="U4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>61</v>
+      </c>
+      <c r="W4" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>3075000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>207</v>
       </c>
     </row>
     <row r="5">
@@ -691,7 +888,12 @@
       <c r="B5" s="2" t="n">
         <v>45542.89583333334</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">soldier field
@@ -739,6 +941,48 @@
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>183</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>575000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>64</v>
+      </c>
+      <c r="W5" t="n">
+        <v>21</v>
+      </c>
+      <c r="X5" t="n">
+        <v>185</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>177</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1850000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>218</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -749,7 +993,12 @@
       <c r="B6" s="2" t="n">
         <v>45542.89583333334</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">shell energy stadium
@@ -797,6 +1046,48 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>175</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>68</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>68</v>
+      </c>
+      <c r="W6" t="n">
+        <v>25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>209</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -807,7 +1098,12 @@
       <c r="B7" s="2" t="n">
         <v>45542.97916666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">bc place
@@ -859,6 +1155,1004 @@
           <t>2i4sdl32</t>
         </is>
       </c>
+      <c r="P7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>175.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>131</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1650000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>134</v>
+      </c>
+      <c r="W7" t="n">
+        <v>23</v>
+      </c>
+      <c r="X7" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>195</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3650000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>A3m1Vera</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>71000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EPngUvhk</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>167</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8lOY3V6E</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>23112</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>QJF7WTFB</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>167</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITj9TZCB</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi field
+  washington  dc </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>167</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lfn5UFc5</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>167</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>8btog05R</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>dKkDSgSH</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chase stadium
+  fort lauderdale  fl </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>21550</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0AheRyBg</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>167</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>vZraQYnO</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vquIRDsO</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inter co stadium
+  orlando  fl </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25500</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>rsHkUNCo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>167</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>jDDw3kMK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.85416666666</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bmo field
+  toronto  on </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30991</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>167</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xUcLQXdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>61500</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>UwAwNo2E</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>167</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EkZQoHSu</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shell energy stadium
+  houston  tx </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>22039</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>167</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>htYUpyrn</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45549.89583333334</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>22423</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4r4sKQud</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>167</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AHSZqech</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45549.9375</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>18061</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>jmBZNRn8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>bm8usLzB</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>167</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>W0ealpQl</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>l8RwqFCb</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>U3ebh62R</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>txUJt9AR</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>167</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>foKU4Bi8</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45549.97916666666</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>54405</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>K2dlua5N</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>167</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1671</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>mls</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,6 +503,76 @@
           <t>id_team_away_rival_team</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -513,7 +583,12 @@
       <c r="B2" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">mercedes benz stadium
@@ -560,6 +635,48 @@
         <is>
           <t>nezMCpx2</t>
         </is>
+      </c>
+      <c r="P2" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>127</v>
+      </c>
+      <c r="U2" t="n">
+        <v>775000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>130</v>
+      </c>
+      <c r="W2" t="n">
+        <v>27.33333333333333</v>
+      </c>
+      <c r="X2" t="n">
+        <v>180</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="3">
@@ -571,7 +688,12 @@
       <c r="B3" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vazquez r 
+  usa </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">saputo stadium
@@ -623,6 +745,34 @@
           <t>nezMCpx2</t>
         </is>
       </c>
+      <c r="P3" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>185</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>67</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>69</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -633,7 +783,12 @@
       <c r="B4" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">audi field
@@ -677,6 +832,48 @@
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>187</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>183</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3250000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>223</v>
+      </c>
+      <c r="W4" t="n">
+        <v>20</v>
+      </c>
+      <c r="X4" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>186</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>4520000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>218</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -687,7 +884,12 @@
       <c r="B5" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">tql stadium
@@ -738,6 +940,48 @@
         <is>
           <t>8btog05R</t>
         </is>
+      </c>
+      <c r="P5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>320</v>
+      </c>
+      <c r="U5" t="n">
+        <v>4835000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>337</v>
+      </c>
+      <c r="W5" t="n">
+        <v>31</v>
+      </c>
+      <c r="X5" t="n">
+        <v>187.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>125</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>525000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>130</v>
       </c>
     </row>
     <row r="6">
@@ -749,7 +993,12 @@
       <c r="B6" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">chase stadium
@@ -800,6 +1049,48 @@
         <is>
           <t>vZraQYnO</t>
         </is>
+      </c>
+      <c r="P6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>148</v>
+      </c>
+      <c r="U6" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>158</v>
+      </c>
+      <c r="W6" t="n">
+        <v>21</v>
+      </c>
+      <c r="X6" t="n">
+        <v>175</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>56</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>275000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="7">
@@ -811,7 +1102,12 @@
       <c r="B7" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso t 
+  usa </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">inter co stadium
@@ -859,6 +1155,48 @@
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>180</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>69</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>69</v>
+      </c>
+      <c r="W7" t="n">
+        <v>24</v>
+      </c>
+      <c r="X7" t="n">
+        <v>179</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -869,7 +1207,12 @@
       <c r="B8" s="2" t="n">
         <v>45549.85416666666</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">penso c 
+  usa </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">bmo field
@@ -920,6 +1263,48 @@
         <is>
           <t>2i4sdl32</t>
         </is>
+      </c>
+      <c r="P8" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>182</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>65</v>
+      </c>
+      <c r="U8" t="n">
+        <v>775000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>67</v>
+      </c>
+      <c r="W8" t="n">
+        <v>23</v>
+      </c>
+      <c r="X8" t="n">
+        <v>188</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>56</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>275000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -931,7 +1316,12 @@
       <c r="B9" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">soldier field
@@ -979,6 +1369,48 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>183</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>64</v>
+      </c>
+      <c r="U9" t="n">
+        <v>575000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>64</v>
+      </c>
+      <c r="W9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>181</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>17600000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -989,7 +1421,12 @@
       <c r="B10" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freemon j 
+  usa </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">shell energy stadium
@@ -1041,6 +1478,34 @@
           <t>jmBZNRn8</t>
         </is>
       </c>
+      <c r="P10" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>176</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>182</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2155000</v>
+      </c>
+      <c r="V10" t="n">
+        <v>203</v>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1051,7 +1516,12 @@
       <c r="B11" s="2" t="n">
         <v>45549.89583333334</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">citypark
@@ -1103,6 +1573,34 @@
           <t>CURGfJWt</t>
         </is>
       </c>
+      <c r="P11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>179.6666666666667</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>201</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3975000</v>
+      </c>
+      <c r="V11" t="n">
+        <v>212</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1113,7 +1611,12 @@
       <c r="B12" s="2" t="n">
         <v>45549.9375</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dujic f 
+  can </t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t xml:space="preserve">dick s sporting goods park
@@ -1164,6 +1667,48 @@
         <is>
           <t>6P5S63Ah</t>
         </is>
+      </c>
+      <c r="P12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>184</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>124</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1675000</v>
+      </c>
+      <c r="V12" t="n">
+        <v>148</v>
+      </c>
+      <c r="W12" t="n">
+        <v>26</v>
+      </c>
+      <c r="X12" t="n">
+        <v>178</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>775000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -1175,7 +1720,12 @@
       <c r="B13" s="2" t="n">
         <v>45549.97916666666</v>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t xml:space="preserve">dignity health sports park
@@ -1219,6 +1769,48 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>169</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="V13" t="n">
+        <v>76</v>
+      </c>
+      <c r="W13" t="n">
+        <v>24</v>
+      </c>
+      <c r="X13" t="n">
+        <v>186</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>129</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>139</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1229,7 +1821,12 @@
       <c r="B14" s="2" t="n">
         <v>45549.97916666666</v>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">szpala l 
+  usa </t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t xml:space="preserve">bc place
@@ -1277,6 +1874,48 @@
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>191</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>50</v>
+      </c>
+      <c r="U14" t="n">
+        <v>110000</v>
+      </c>
+      <c r="V14" t="n">
+        <v>70</v>
+      </c>
+      <c r="W14" t="n">
+        <v>27</v>
+      </c>
+      <c r="X14" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>138</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1287,7 +1926,12 @@
       <c r="B15" s="2" t="n">
         <v>45550.84375</v>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">lumen field
@@ -1339,788 +1983,48 @@
           <t>2i4sdl32</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>dYUosgsB</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>71000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0AheRyBg</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>167</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>U3Cs29yR</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gillette stadium
-  foxborough  ma </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>68756</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>167</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>vcKjtDdH</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yankee stadium
-  new york  ny </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>54251</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Szrwix67</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>167</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Me49cTqr</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45553.85416666666</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>30991</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>167</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>ImJfuXBN</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45553.88541666666</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>25500</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>QJF7WTFB</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>167</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>0n3Ddmal</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>22039</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>167</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SM4QZAZp</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz field
-  saint paul  mn </t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>19400</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>167</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>URr9bfCo</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>84yIDQMe</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>167</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>QDIbviRT</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>45553.89583333334</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>21650</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>167</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>rVnDcERi</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>45553.9375</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>20213</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>167</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xhnHdYtb</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bmo stadium
-  los angeles  ca </t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>22000</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>txUJt9AR</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>IeT6JBE3</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>167</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>GroLehd4</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">providence park
-  portland  or </t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>25218</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>U3ebh62R</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>167</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YJuQfCBA</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="n">
-        <v>45553.97916666666</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>x05z14ue</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>167</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>33.66666666666666</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>177</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>222</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8650000</v>
+      </c>
+      <c r="V15" t="n">
+        <v>222</v>
+      </c>
+      <c r="W15" t="n">
+        <v>26</v>
+      </c>
+      <c r="X15" t="n">
+        <v>184</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>208</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,42 +515,42 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_rat_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_home</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_miss_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_miss_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_wage_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
@@ -561,51 +561,41 @@
       <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>sum_val_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>A3m1Vera</t>
+          <t>CAvUgWQG</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">villarreal a 
+          <t xml:space="preserve">freemon j 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mercedes benz stadium
-  atlanta  ga </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>71000</v>
+        <v>54251</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>0AheRyBg</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -633,84 +623,76 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>31</v>
+        <v>22.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>176.5</v>
+        <v>180.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
-        <v>127</v>
-      </c>
       <c r="U2" t="n">
-        <v>775000</v>
+        <v>111</v>
       </c>
       <c r="V2" t="n">
-        <v>130</v>
+        <v>23.6</v>
       </c>
       <c r="W2" t="n">
-        <v>27.33333333333333</v>
+        <v>181</v>
       </c>
       <c r="X2" t="n">
-        <v>180</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>6000</v>
       </c>
       <c r="Z2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>200</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8lOY3V6E</t>
+          <t>6XwYhjtN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.70833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vazquez r 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">bank of america stadium
+  charlotte  nc </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>23112</v>
+        <v>74867</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>QJF7WTFB</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>QJF7WTFB</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -737,75 +719,67 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
           <t>nezMCpx2</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>185</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>67</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1100000</v>
-      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>69</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="W3" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ITj9TZCB</t>
+          <t>rBhIe7Ef</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">touchan r 
+          <t xml:space="preserve">szpala l 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi field
-  washington  dc </t>
+          <t xml:space="preserve">saputo stadium
+  montreal  qc </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20000</v>
+        <v>23112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>O6hjfSXE</t>
+          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>UwAwNo2E</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -830,83 +804,73 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>187</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>183</v>
-      </c>
-      <c r="U4" t="n">
-        <v>3250000</v>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>zsdfgnmL</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>tr3oe8I8</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>223</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="W4" t="n">
-        <v>20</v>
+        <v>182.6666666666667</v>
       </c>
       <c r="X4" t="n">
-        <v>181.3333333333333</v>
+        <v>67.66666666666667</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>3666.666666666667</v>
       </c>
       <c r="Z4" t="n">
         <v>3</v>
       </c>
       <c r="AA4" t="n">
-        <v>186</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>4520000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lfn5UFc5</t>
+          <t>I7sxhAeT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dickerson j 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">tql stadium
-  cincinnati  oh </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26000</v>
+        <v>20371</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>rsHkUNCo</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -933,89 +897,81 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>8btog05R</t>
+          <t>nezMCpx2</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="Q5" t="n">
-        <v>186.8</v>
+        <v>186</v>
       </c>
       <c r="R5" t="n">
+        <v>63</v>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
         <v>1</v>
       </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>320</v>
-      </c>
       <c r="U5" t="n">
-        <v>4835000</v>
+        <v>63</v>
       </c>
       <c r="V5" t="n">
-        <v>337</v>
+        <v>25</v>
       </c>
       <c r="W5" t="n">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="X5" t="n">
-        <v>187.5</v>
+        <v>58</v>
       </c>
       <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
         <v>1</v>
       </c>
-      <c r="Z5" t="n">
-        <v>2</v>
-      </c>
       <c r="AA5" t="n">
-        <v>125</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>525000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>130</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dKkDSgSH</t>
+          <t>OlK4mU3p</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">penso c 
+  usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">chase stadium
-  fort lauderdale  fl </t>
+          <t xml:space="preserve">red bull arena
+  harrison  nj </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21550</v>
+        <v>25000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
+          <t>zV5YmQAr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Szrwix67</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1040,91 +996,75 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>vZraQYnO</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>24.5</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="Q6" t="n">
-        <v>178.5</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>65.66666666666667</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>20666.66666666667</v>
       </c>
       <c r="T6" t="n">
-        <v>148</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>15000000</v>
+        <v>197</v>
       </c>
       <c r="V6" t="n">
-        <v>158</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>21</v>
+        <v>176.6666666666667</v>
       </c>
       <c r="X6" t="n">
-        <v>175</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
+        <v>64.66666666666667</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>56</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>275000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>63</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vquIRDsO</t>
+          <t>2uJ8nlJj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso t 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">inter co stadium
-  orlando  fl </t>
+          <t xml:space="preserve">q2 stadium
+  austin  tx </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25500</v>
+        <v>20738</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>rsHkUNCo</t>
+          <t>IeT6JBE3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1151,85 +1091,69 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>180</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>69</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1200000</v>
-      </c>
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>69</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="W7" t="n">
-        <v>24</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="X7" t="n">
-        <v>179</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>78</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jDDw3kMK</t>
+          <t>jeCjBXei</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45549.85416666666</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bmo field
-  toronto  on </t>
+          <t xml:space="preserve">toyota stadium
+  frisco  tx </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30991</v>
+        <v>20500</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
+          <t>4GtbI4Q1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>txUJt9AR</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1256,89 +1180,77 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
           <t>2i4sdl32</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>182</v>
+        <v>177.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>65.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="T8" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>775000</v>
+        <v>131</v>
       </c>
       <c r="V8" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="W8" t="n">
-        <v>23</v>
+        <v>186</v>
       </c>
       <c r="X8" t="n">
-        <v>188</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1</v>
-      </c>
+        <v>64.5</v>
+      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>56</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>275000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>63</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>xUcLQXdU</t>
+          <t>CA0a9BQ3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
-  usa </t>
+          <t xml:space="preserve">lauziere p 
+  can </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">soldier field
-  chicago  il </t>
+          <t xml:space="preserve">geodis park
+  nashville  tn </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>61500</v>
+        <v>30000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
+          <t>84yIDQMe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1365,85 +1277,81 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>nezMCpx2</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>pQ8rarA7</t>
+        </is>
+      </c>
       <c r="P9" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>66</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>132</v>
+      </c>
+      <c r="V9" t="n">
         <v>27</v>
       </c>
-      <c r="Q9" t="n">
-        <v>183</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T9" t="n">
-        <v>64</v>
-      </c>
-      <c r="U9" t="n">
-        <v>575000</v>
-      </c>
-      <c r="V9" t="n">
-        <v>64</v>
-      </c>
       <c r="W9" t="n">
-        <v>25.5</v>
+        <v>181.4</v>
       </c>
       <c r="X9" t="n">
-        <v>181</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA9" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>141</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>EkZQoHSu</t>
+          <t>UoBfAiBc</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.89583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">pekmic i 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">shell energy stadium
-  houston  tx </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>22039</v>
+        <v>21650</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>zXFxsw2a</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1470,75 +1378,83 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>2i4sdl32</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>23.33333333333333</v>
+        <v>27</v>
       </c>
       <c r="Q10" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="R10" t="n">
+        <v>64</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>182</v>
-      </c>
       <c r="U10" t="n">
-        <v>2155000</v>
+        <v>64</v>
       </c>
       <c r="V10" t="n">
-        <v>203</v>
-      </c>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+        <v>32.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>187</v>
+      </c>
+      <c r="X10" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>htYUpyrn</t>
+          <t>tdBLfRT0</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45549.89583333334</v>
+        <v>45556.9375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">de oliveira m 
+          <t xml:space="preserve">mendoza r 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">citypark
-  st  louis  mo </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22423</v>
+        <v>18061</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
+          <t>zsdfgnmL</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1565,70 +1481,66 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="R11" t="n">
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>32</v>
+      </c>
+      <c r="W11" t="n">
+        <v>190</v>
+      </c>
+      <c r="X11" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1</v>
       </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>201</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3975000</v>
-      </c>
-      <c r="V11" t="n">
-        <v>212</v>
-      </c>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AHSZqech</t>
+          <t>QD438VuA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45549.9375</v>
+        <v>45556.9375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dujic f 
-  can </t>
+          <t xml:space="preserve">penso t 
+  usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">america first field
+  sandy  ut </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>18061</v>
+        <v>20213</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>W0ealpQl</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1660,7 +1572,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>W0ealpQl</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1668,61 +1580,31 @@
           <t>6P5S63Ah</t>
         </is>
       </c>
-      <c r="P12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>184</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>124</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1675000</v>
-      </c>
-      <c r="V12" t="n">
-        <v>148</v>
-      </c>
-      <c r="W12" t="n">
-        <v>26</v>
-      </c>
-      <c r="X12" t="n">
-        <v>178</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>775000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>65</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l8RwqFCb</t>
+          <t>zJAPgoq7</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">unkel t 
+          <t xml:space="preserve">marrufo j 
   usa </t>
         </is>
       </c>
@@ -1742,7 +1624,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>txUJt9AR</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -1768,82 +1650,80 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q13" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="R13" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2500</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>137</v>
+      </c>
+      <c r="V13" t="n">
+        <v>22</v>
+      </c>
+      <c r="W13" t="n">
+        <v>180</v>
+      </c>
+      <c r="X13" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V13" t="n">
-        <v>76</v>
-      </c>
-      <c r="W13" t="n">
-        <v>24</v>
-      </c>
-      <c r="X13" t="n">
-        <v>186</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2</v>
-      </c>
       <c r="AA13" t="n">
-        <v>129</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>139</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>foKU4Bi8</t>
+          <t>Kz477keG</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45549.97916666666</v>
+        <v>45556.97916666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
-  usa </t>
+          <t xml:space="preserve">montero r 
+  cos </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">bc place
-  vancouver  bc </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>54405</v>
+        <v>18000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
+          <t>x05z14ue</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -1868,162 +1748,47 @@
           <t>mls</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>CURGfJWt</t>
+        </is>
+      </c>
       <c r="P14" t="n">
-        <v>18</v>
+        <v>26.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>191</v>
+        <v>183.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>71.5</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>6250</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>110000</v>
+        <v>286</v>
       </c>
       <c r="V14" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="W14" t="n">
-        <v>27</v>
+        <v>179.6666666666667</v>
       </c>
       <c r="X14" t="n">
-        <v>180.5</v>
+        <v>67</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>3333.333333333333</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>138</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rVQsrZR4</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45550.84375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fischer d 
-  can </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lumen field
-  seattle  wa </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>167</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1671</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>mls</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>33.66666666666666</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>177</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>222</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8650000</v>
-      </c>
-      <c r="V15" t="n">
-        <v>222</v>
-      </c>
-      <c r="W15" t="n">
-        <v>26</v>
-      </c>
-      <c r="X15" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>199</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>3800000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
+++ b/data/usa/p6_deployment/data_preparation/df_integrated.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:BG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,214 +465,476 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_home_rival_team</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_away_rival_team</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_miss_home</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_miss_home</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_miss_away</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CAvUgWQG</t>
+          <t>YuZ4CywD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45556.625</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">freemon j 
+          <t xml:space="preserve">pekmic i 
   usa </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">yankee stadium
-  new york  ny </t>
+          <t xml:space="preserve">mercedes benz stadium
+  atlanta  ga </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54251</v>
+        <v>71000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>vZraQYnO</t>
+          <t>EPngUvhk</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0AheRyBg</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+          <t>zV5YmQAr</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>167</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>1671</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>2024</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>rsHkUNCo</t>
-        </is>
-      </c>
       <c r="P2" t="n">
-        <v>22.5</v>
+        <v>28.22222222222222</v>
       </c>
       <c r="Q2" t="n">
-        <v>180.5</v>
+        <v>180.2222222222222</v>
       </c>
       <c r="R2" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
+        <v>66.77777777777777</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5666.666666666667</v>
+      </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1160000</v>
       </c>
       <c r="U2" t="n">
-        <v>111</v>
+        <v>69.11111111111111</v>
       </c>
       <c r="V2" t="n">
-        <v>23.6</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>5400</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2177500</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>180.5555555555555</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>62.33333333333334</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>4666.666666666667</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>737777.7777777778</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>67.44444444444444</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>24.125</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>181.125</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>63</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5375</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2348125</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>176</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>265</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3575000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>268</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>180.6666666666667</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC2" t="n">
         <v>181</v>
       </c>
-      <c r="X2" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>357</v>
+      <c r="BD2" t="n">
+        <v>14000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>2510000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>202</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6XwYhjtN</t>
+          <t>UuWb8pb0</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45556.70833333334</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">allatin m 
+          <t xml:space="preserve">rivas v 
   usa </t>
         </is>
       </c>
@@ -692,180 +954,400 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+          <t>j9cigLCr</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>167</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1671</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>2024</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>27.875</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="R3" t="n">
+        <v>69.625</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6125</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2562500</v>
+      </c>
+      <c r="U3" t="n">
+        <v>73.25</v>
+      </c>
       <c r="V3" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>178.5</v>
+        <v>23.63636363636364</v>
       </c>
       <c r="X3" t="n">
-        <v>68.5</v>
+        <v>177.3636363636364</v>
       </c>
       <c r="Y3" t="n">
-        <v>4500</v>
+        <v>65.72727272727273</v>
       </c>
       <c r="Z3" t="n">
+        <v>5090.909090909091</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1370454.545454545</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>73</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5625</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1440000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>182.1428571428571</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>64.85714285714286</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>8428.571428571429</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1590714.285714286</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>73.28571428571429</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AT3" t="n">
         <v>2</v>
       </c>
-      <c r="AA3" t="n">
-        <v>137</v>
+      <c r="AU3" t="n">
+        <v>123</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1875000</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>144</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>183</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>66</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>67</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rBhIe7Ef</t>
+          <t>llHizuVJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">szpala l 
+          <t xml:space="preserve">chapman a 
   usa </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">saputo stadium
-  montreal  qc </t>
+          <t xml:space="preserve">lower com field
+  columbus  oh </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>23112</v>
+        <v>20371</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>j9cigLCr</t>
+          <t>pQ8rarA7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UwAwNo2E</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
+          <t>Szrwix67</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>167</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1671</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2024</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>tr3oe8I8</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>180.2222222222222</v>
+      </c>
+      <c r="R4" t="n">
+        <v>71.11111111111111</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4608333.333333333</v>
+      </c>
+      <c r="U4" t="n">
+        <v>74.11111111111111</v>
+      </c>
       <c r="V4" t="n">
-        <v>28.66666666666667</v>
+        <v>1</v>
       </c>
       <c r="W4" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2810000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>23.66666666666667</v>
+      </c>
+      <c r="AE4" t="n">
         <v>182.6666666666667</v>
       </c>
-      <c r="X4" t="n">
-        <v>67.66666666666667</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3666.666666666667</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AF4" t="n">
+        <v>63</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>4833.333333333333</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>875000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>62.25</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>905625</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>69.375</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>31.66666666666667</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="AT4" t="n">
         <v>3</v>
       </c>
-      <c r="AA4" t="n">
-        <v>203</v>
+      <c r="AU4" t="n">
+        <v>197</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2720000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>205</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>175</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>56</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>275000</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>63</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>I7sxhAeT</t>
+          <t>CWX8BehJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">boiko s 
-  ukr </t>
+          <t xml:space="preserve">dujic f 
+  can </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lower com field
-  columbus  oh </t>
+          <t xml:space="preserve">tql stadium
+  cincinnati  oh </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20371</v>
+        <v>26000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pQ8rarA7</t>
+          <t>8btog05R</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -873,282 +1355,580 @@
           <t>rsHkUNCo</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>167</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>1671</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>2024</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
       <c r="P5" t="n">
-        <v>37</v>
+        <v>26.45454545454545</v>
       </c>
       <c r="Q5" t="n">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="R5" t="n">
-        <v>63</v>
+        <v>70.81818181818181</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>4500000</v>
       </c>
       <c r="U5" t="n">
-        <v>63</v>
+        <v>74.36363636363636</v>
       </c>
       <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>28</v>
+      </c>
+      <c r="X5" t="n">
+        <v>179.5454545454545</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>69.63636363636364</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>6545.454545454545</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2540909.090909091</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>72.09090909090909</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.090909090909091</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>24.55555555555556</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>181.8888888888889</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>61.55555555555556</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5111.111111111111</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1038888.888888889</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>66.77777777777777</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>4833.333333333333</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>945833.3333333334</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>68</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>28.25</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>252</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>2225000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>262</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>25</v>
       </c>
-      <c r="W5" t="n">
-        <v>188</v>
-      </c>
-      <c r="X5" t="n">
-        <v>58</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>58</v>
+      <c r="BA5" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>192</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>14000</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>3410000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>207</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OlK4mU3p</t>
+          <t>pK2NUIhs</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45556.85416666666</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso c 
+          <t xml:space="preserve">da silva a 
   usa </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  harrison  nj </t>
+          <t xml:space="preserve">gillette stadium
+  foxborough  ma </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25000</v>
+        <v>68756</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>zV5YmQAr</t>
+          <t>tr3oe8I8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EPngUvhk</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
+          <t>O6hjfSXE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>167</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>1671</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>2024</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>25.33333333333333</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="R6" t="n">
-        <v>65.66666666666667</v>
-      </c>
-      <c r="S6" t="n">
-        <v>20666.66666666667</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3</v>
-      </c>
-      <c r="U6" t="n">
-        <v>197</v>
-      </c>
-      <c r="V6" t="n">
-        <v>29.33333333333333</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>176.6666666666667</v>
+        <v>27.90909090909091</v>
       </c>
       <c r="X6" t="n">
-        <v>64.66666666666667</v>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+        <v>181.1818181818182</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>68.36363636363636</v>
+      </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>6181.818181818182</v>
       </c>
       <c r="AA6" t="n">
-        <v>194</v>
+        <v>1438636.363636364</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>71.63636363636364</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>180.3</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5800</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>949000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>183.5714285714286</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>60.57142857142857</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5142.857142857143</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>541428.5714285715</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>65.85714285714286</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>138</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>8250000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>147</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>189</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>109</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>650000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>148</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2uJ8nlJj</t>
+          <t>MFWf9Qrf</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.85416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">rivas v 
+          <t xml:space="preserve">touchan r 
   usa </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">q2 stadium
-  austin  tx </t>
+          <t xml:space="preserve">bc place
+  vancouver  bc </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20738</v>
+        <v>54405</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>IeT6JBE3</t>
+          <t>K2dlua5N</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
+          <t>zXFxsw2a</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>167</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1671</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>2024</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>4GtbI4Q1</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>26.11111111111111</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>177.1111111111111</v>
+      </c>
+      <c r="R7" t="n">
+        <v>70</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6444.444444444444</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3338888.888888889</v>
+      </c>
+      <c r="U7" t="n">
+        <v>73.33333333333333</v>
+      </c>
       <c r="V7" t="n">
-        <v>20.33333333333333</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>183.6666666666667</v>
+        <v>25.44444444444444</v>
       </c>
       <c r="X7" t="n">
-        <v>56</v>
-      </c>
-      <c r="Y7" t="inlineStr"/>
+        <v>181.8888888888889</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>64.88888888888889</v>
+      </c>
       <c r="Z7" t="n">
+        <v>5555.555555555556</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1173888.888888889</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>69.77777777777777</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>179.375</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5125</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>806250</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>68</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>180.1428571428571</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>60.71428571428572</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5285.714285714285</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1176428.571428571</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>66.28571428571429</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="AT7" t="n">
         <v>3</v>
       </c>
-      <c r="AA7" t="n">
-        <v>168</v>
+      <c r="AU7" t="n">
+        <v>182</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1885000</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>206</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>30.66666666666667</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>178.6666666666667</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>204</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>21000</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3375000</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>205</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jeCjBXei</t>
+          <t>r5LQTx8m</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.89583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">da silva a 
+          <t xml:space="preserve">de oliveira m 
   usa </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">toyota stadium
-  frisco  tx </t>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20500</v>
+        <v>21650</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4GtbI4Q1</t>
+          <t>CURGfJWt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1156,337 +1936,433 @@
           <t>txUJt9AR</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>167</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1671</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>2024</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>177.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>131</v>
-      </c>
-      <c r="V8" t="n">
-        <v>24</v>
-      </c>
-      <c r="W8" t="n">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>31.33333333333333</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>182</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>212</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4150000</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>212</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA8" t="n">
         <v>186</v>
       </c>
-      <c r="X8" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>129</v>
+      <c r="BB8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>201</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2675000</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>211</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CA0a9BQ3</t>
+          <t>QTAVSdNg</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.89583333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">lauziere p 
-  can </t>
+          <t xml:space="preserve">penso t 
+  usa </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">geodis park
-  nashville  tn </t>
+          <t xml:space="preserve">citypark
+  st  louis  mo </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30000</v>
+        <v>22423</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>84yIDQMe</t>
+          <t>4r4sKQud</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8btog05R</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
+          <t>2i4sdl32</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
         <v>167</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>1671</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>2024</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>nezMCpx2</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>pQ8rarA7</t>
-        </is>
-      </c>
-      <c r="P9" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>66</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3500</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>177</v>
+      </c>
+      <c r="AT9" t="n">
         <v>2</v>
       </c>
-      <c r="U9" t="n">
-        <v>132</v>
-      </c>
-      <c r="V9" t="n">
+      <c r="AU9" t="n">
+        <v>131</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>142</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>27</v>
       </c>
-      <c r="W9" t="n">
-        <v>181.4</v>
-      </c>
-      <c r="X9" t="n">
-        <v>66</v>
-      </c>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>330</v>
+      <c r="BA9" t="n">
+        <v>179</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>127</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>137</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UoBfAiBc</t>
+          <t>4K9ZRGx0</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45556.89583333334</v>
+        <v>45570.9375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">pekmic i 
+          <t xml:space="preserve">ford t 
   usa </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">children s mercy park
-  kansas city  ks </t>
+          <t xml:space="preserve">dick s sporting goods park
+  commerce city  co </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>21650</v>
+        <v>18061</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CURGfJWt</t>
+          <t>jmBZNRn8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>zXFxsw2a</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
+          <t>6P5S63Ah</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
         <v>167</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>1671</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>2024</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2i4sdl32</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>188</v>
-      </c>
-      <c r="R10" t="n">
-        <v>64</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>64</v>
-      </c>
-      <c r="V10" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>187</v>
-      </c>
-      <c r="X10" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1500</v>
-      </c>
-      <c r="Z10" t="n">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AT10" t="n">
         <v>2</v>
       </c>
-      <c r="AA10" t="n">
-        <v>127</v>
+      <c r="AU10" t="n">
+        <v>134</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11000</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>145</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>33</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>171</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>76</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>9000</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>76</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tdBLfRT0</t>
+          <t>YgEwRzh6</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45570.97916666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">mendoza r 
+          <t xml:space="preserve">unkel t 
   usa </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dick s sporting goods park
-  commerce city  co </t>
+          <t xml:space="preserve">dignity health sports park
+  carson  ca </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18061</v>
+        <v>27000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>jmBZNRn8</t>
+          <t>U3ebh62R</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>zsdfgnmL</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+          <t>IeT6JBE3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
         <v>167</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>1671</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>2024</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>W0ealpQl</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>j9cigLCr</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1495,89 +2371,117 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>32</v>
-      </c>
-      <c r="W11" t="n">
-        <v>190</v>
-      </c>
-      <c r="X11" t="n">
-        <v>69</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>8000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>69</v>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>165</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>68</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7000</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>68</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>QD438VuA</t>
+          <t>CpDsQf7C</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45556.9375</v>
+        <v>45570.97916666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">penso t 
+          <t xml:space="preserve">allatin m 
   usa </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">america first field
-  sandy  ut </t>
+          <t xml:space="preserve">paypal park
+  san jose  ca </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20213</v>
+        <v>18000</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>x05z14ue</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>W0ealpQl</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>bm8usLzB</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
         <v>167</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1671</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>2024</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>mls</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>jmBZNRn8</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -1592,203 +2496,339 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>318</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>25000</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>342</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>180</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>69</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>6000</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>73</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>zJAPgoq7</t>
+          <t>SvGeZbpQ</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45571.70833333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">marrufo j 
-  usa </t>
+          <t xml:space="preserve">boiko s 
+  ukr </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dignity health sports park
-  carson  ca </t>
+          <t xml:space="preserve">yankee stadium
+  new york  ny </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>27000</v>
+        <v>54251</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>U3ebh62R</t>
+          <t>vZraQYnO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>K2dlua5N</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
+          <t>84yIDQMe</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
         <v>167</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>1671</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>2024</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>6P5S63Ah</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>180</v>
-      </c>
-      <c r="R13" t="n">
-        <v>68.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2500</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>137</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
         <v>22</v>
       </c>
-      <c r="W13" t="n">
-        <v>180</v>
-      </c>
-      <c r="X13" t="n">
-        <v>62</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>62</v>
+      <c r="AS13" t="n">
+        <v>182.3333333333333</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>189</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3810000</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>209</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>183</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>200</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>19000</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>200</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Kz477keG</t>
+          <t>f92nPEMI</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45556.97916666666</v>
+        <v>45571.83333333334</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">montero r 
-  cos </t>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">paypal park
-  san jose  ca </t>
+          <t xml:space="preserve">providence park
+  portland  or </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>18000</v>
+        <v>25218</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>x05z14ue</t>
+          <t>bm8usLzB</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4r4sKQud</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
+          <t>4GtbI4Q1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
         <v>167</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>1671</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>2024</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>usa</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>mls</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>CURGfJWt</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="R14" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="S14" t="n">
-        <v>6250</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4</v>
-      </c>
-      <c r="U14" t="n">
-        <v>286</v>
-      </c>
-      <c r="V14" t="n">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
         <v>25</v>
       </c>
-      <c r="W14" t="n">
-        <v>179.6666666666667</v>
-      </c>
-      <c r="X14" t="n">
-        <v>67</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3333.333333333333</v>
-      </c>
-      <c r="Z14" t="n">
+      <c r="AS14" t="n">
+        <v>191</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>66</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>6000</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>69</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>180</v>
+      </c>
+      <c r="BB14" t="n">
         <v>3</v>
       </c>
-      <c r="AA14" t="n">
-        <v>201</v>
+      <c r="BC14" t="n">
+        <v>194</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>17000</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>3350000</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>211</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
